--- a/prop/translation/data-services.xlsx
+++ b/prop/translation/data-services.xlsx
@@ -41,7 +41,7 @@
     <t>Three Data Access Options</t>
   </si>
   <si>
-    <t>三种数据获取模式</t>
+    <t>数据资源矩阵</t>
   </si>
   <si>
     <t>Open Source</t>
@@ -191,7 +191,7 @@
     <t>Tightly aligned multi-view visual streams give models a consistent temporal foundation for perception, fusion, and action learning.</t>
   </si>
   <si>
-    <t>高度对齐的多视角视觉流，为感知、融合与动作学习提供一致的时空一致性基础</t>
+    <t>高度对齐的多视角视觉流，为感知融合与动作学习提供一致的时空一致性基础</t>
   </si>
   <si>
     <t>0x03</t>
@@ -215,7 +215,7 @@
     <t>RealSource pairs dense robot proprioception with large-scale visual demonstrations to support both learning and evaluation workflows.</t>
   </si>
   <si>
-    <t>将高密度机器人本体感知与大规模视觉示教深度融合，完美支持训练与评估流程</t>
+    <t>将高密度机器人本体感知与大规模视觉数据深度融合，完美支持训练与评估流程</t>
   </si>
   <si>
     <t>0x04</t>
@@ -245,7 +245,7 @@
     <t>For the same task, large-scale demonstrations are performed across diverse variables, including object attributes, environmental context, motion trajectories, and viewpoints, to support broader generalization.</t>
   </si>
   <si>
-    <t>围绕同一任务，在物体属性、环境上下文、运动轨迹与视角等多种变量下开展大规模示教，支撑更强的算法泛化能力</t>
+    <t>围绕同一任务，在物体属性、环境上下文、运动轨迹与视角等多种变量下开展大规模泛化采集，支撑更强的算法泛化能力</t>
   </si>
   <si>
     <t>0x02</t>
@@ -269,7 +269,7 @@
     <t>An optimized transmission, caching, and processing pipeline helps preserve complete and continuous demonstrations even under demanding recording conditions.</t>
   </si>
   <si>
-    <t>经过优化的传输、缓存与处理链路，即使在高强度采集条件下，也能确保示教数据的完整性与连续性</t>
+    <t>经过优化的传输、缓存与处理链路，即使在高强度采集条件下，也能确保数据的完整性与连续性</t>
   </si>
   <si>
     <t>0x06</t>
@@ -278,7 +278,7 @@
     <t>7 DoF</t>
   </si>
   <si>
-    <t>7 自由度</t>
+    <t>7 自由度外骨骼遥操</t>
   </si>
   <si>
     <t>Human-Like Demonstrations at the Source</t>
@@ -296,7 +296,7 @@
     <t>Exoskeleton-based teleoperation preserves natural dual-arm coordination and expert motion intent, creating trajectories that are more transferable to real embodied tasks.</t>
   </si>
   <si>
-    <t>高度还原人类操作员的双臂协同与专家动作意图，生成更适用于真实具身任务的高质量轨迹数据</t>
+    <t>高度还原人类操作员的双臂协同动作意图及决策过程，生成更适用于真实具身任务的高质量轨迹数据</t>
   </si>
   <si>
     <t>Standards &amp; Interoperability</t>
@@ -462,7 +462,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,13 +474,6 @@
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -969,148 +962,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
